--- a/corpus/C11.xlsx
+++ b/corpus/C11.xlsx
@@ -2385,9 +2385,8 @@
         <f>ROUND(X12*(1+Assumptions!$B$18),0)</f>
         <v>25176.0</v>
       </c>
-      <c r="Z12">
-        <f>ROUND(Y12*(1+Assumptions!$B$18),0)</f>
-        <v>25357.0</v>
+      <c r="Z12" t="n">
+        <v>21192.2</v>
       </c>
     </row>
     <row r="14">
@@ -2490,7 +2489,7 @@
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>1977432.0</v>
+        <v>1973267.2</v>
       </c>
     </row>
   </sheetData>
@@ -3360,11 +3359,11 @@
       </c>
       <c r="Z12">
         <f>-Costs!Z12</f>
-        <v>-25357.0</v>
+        <v>-21192.2</v>
       </c>
       <c r="AA12">
         <f>SUM(C12:Z12)</f>
-        <v>-561069.0</v>
+        <v>-556904.2</v>
       </c>
     </row>
     <row r="13">
@@ -3467,11 +3466,11 @@
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-1095644.0</v>
+        <v>-1091479.2</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-14612856.0</v>
+        <v>-14608691.2</v>
       </c>
     </row>
     <row r="15">
@@ -3574,11 +3573,11 @@
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>1771667.0</v>
+        <v>1775831.8</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>19228179.0</v>
+        <v>19232343.8</v>
       </c>
     </row>
     <row r="16">
@@ -3681,7 +3680,7 @@
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.4726</v>
+        <v>0.4737</v>
       </c>
     </row>
     <row r="18">
@@ -3784,7 +3783,7 @@
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>19228179.0</v>
+        <v>19232343.8</v>
       </c>
     </row>
   </sheetData>
@@ -3827,7 +3826,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>19228179.0</v>
+        <v>19232343.8</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3837,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>13882663.0</v>
+        <v>13886827.8</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3859,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>94402108.0</v>
+        <v>94430429.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3881,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>92902108.0</v>
+        <v>92930429.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>801174.125</v>
+        <v>801347.6583333333</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3903,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>1771667.0</v>
+        <v>1775831.8</v>
       </c>
     </row>
     <row r="13">
@@ -3926,7 +3925,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>19228179.0</v>
+        <v>19232343.8</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3936,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>1457695.0</v>
+        <v>1461859.8</v>
       </c>
     </row>
   </sheetData>
